--- a/docs/CodeSystem-no-kodeverk-8660.xlsx
+++ b/docs/CodeSystem-no-kodeverk-8660.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-19T20:08:40+02:00</t>
+    <t>2025-10-31T08:54:10+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
